--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1016,7 +1016,7 @@
 </t>
   </si>
   <si>
-    <t>Date/Time this version was made available</t>
+    <t>The mandatory date/time this version was made available</t>
   </si>
   <si>
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile can be used for all the other Observations for PreNUDGE, beeing quantities and not fitting the existing narrow standardized observations. If some code for specifing a new Observation is missing, please contact prenudge@joanneum.at.</t>
+    <t>This FHIR profile can be used for all the other Observations for PreNUDGE, beeing quantities and not fitting the existing narrow standardized observations. If some code for specifying a new Observation is missing, please contact prenudge@joanneum.at.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1234,7 +1234,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the result is missing</t>
+    <t>Reason why no clinically or analytically meaningful result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
@@ -1720,7 +1720,7 @@
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the component result is missing</t>
+    <t>Reason why no clinically or analytically meaningful component result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
@@ -6816,7 +6816,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>391</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -9828,7 +9828,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>545</v>
       </c>
@@ -9847,7 +9847,7 @@
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
